--- a/Problem8_Roll_Rate_Modeling/reports/financial_impact_reporting_packaging/AMEX_Problem8_Financial_Impact_Workbook.xlsx
+++ b/Problem8_Roll_Rate_Modeling/reports/financial_impact_reporting_packaging/AMEX_Problem8_Financial_Impact_Workbook.xlsx
@@ -22,11 +22,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -129,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,7 +146,7 @@
     <xf numFmtId="3" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -154,16 +160,24 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -714,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -724,6 +738,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -735,6 +750,13 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Comprehensive Financial Impact Summary (Phase 3 Close-Out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
         </is>
       </c>
     </row>
@@ -767,7 +789,7 @@
           <t>Net Benefit / Cycle</t>
         </is>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="20">
         <f>'Escalation Impact'!B10</f>
         <v/>
       </c>
@@ -880,7 +902,7 @@
           <t>Ead Per Account Usd</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="21" t="n">
         <v>5000</v>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -895,7 +917,7 @@
           <t>Lgd Assumption</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="22" t="n">
         <v>0.45</v>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -910,7 +932,7 @@
           <t>Escalation Intervention Success Rate</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="22" t="n">
         <v>0.18</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -925,7 +947,7 @@
           <t>False Positive Review Cost Usd</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="21" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -940,7 +962,7 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="21" t="n">
         <v>40000</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -1043,7 +1065,7 @@
           <t>Real Defaulter Capture Rate Among Escalated</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="23" t="n">
         <v>0.03976812582583863</v>
       </c>
     </row>
@@ -1064,7 +1086,7 @@
           <t>Gross Loss Prevented / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="24">
         <f>B7*Assumptions!$B$2*Assumptions!$B$3</f>
         <v/>
       </c>
@@ -1075,7 +1097,7 @@
           <t>False-Positive Review Cost / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="24">
         <f>B5*Assumptions!$B$5</f>
         <v/>
       </c>
@@ -1086,7 +1108,7 @@
           <t>Net Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="24">
         <f>B8-B9</f>
         <v/>
       </c>
@@ -1097,7 +1119,7 @@
           <t>Annual Net Benefit (USD)</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="24">
         <f>B10*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -1256,7 +1278,7 @@
       <c r="B2" t="n">
         <v>29064</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="23" t="n">
         <v>0.3166599479206389</v>
       </c>
       <c r="D2" t="n">
@@ -1275,7 +1297,7 @@
       <c r="B3" t="n">
         <v>28435</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="23" t="n">
         <v>0.3098068269723152</v>
       </c>
       <c r="D3" t="n">
@@ -1294,7 +1316,7 @@
       <c r="B4" t="n">
         <v>34284</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="23" t="n">
         <v>0.373533225107046</v>
       </c>
       <c r="D4" t="n">
